--- a/AAII_Financials/Yearly/SCCTY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SCCTY_YR_FIN.xlsx
@@ -714,25 +714,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>786000</v>
+        <v>762700</v>
       </c>
       <c r="E8" s="3">
-        <v>609600</v>
+        <v>586300</v>
       </c>
       <c r="F8" s="3">
-        <v>587900</v>
+        <v>562700</v>
       </c>
       <c r="G8" s="3">
-        <v>509000</v>
+        <v>478300</v>
       </c>
       <c r="H8" s="3">
-        <v>472700</v>
+        <v>442400</v>
       </c>
       <c r="I8" s="3">
-        <v>459700</v>
+        <v>432800</v>
       </c>
       <c r="J8" s="3">
-        <v>408200</v>
+        <v>392500</v>
       </c>
       <c r="K8" s="3">
         <v>377200</v>
@@ -780,25 +780,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>590000</v>
+        <v>566600</v>
       </c>
       <c r="E10" s="3">
-        <v>461600</v>
+        <v>438400</v>
       </c>
       <c r="F10" s="3">
-        <v>461800</v>
+        <v>436600</v>
       </c>
       <c r="G10" s="3">
-        <v>394300</v>
+        <v>363600</v>
       </c>
       <c r="H10" s="3">
-        <v>361600</v>
+        <v>331400</v>
       </c>
       <c r="I10" s="3">
-        <v>361600</v>
+        <v>334700</v>
       </c>
       <c r="J10" s="3">
-        <v>287400</v>
+        <v>271700</v>
       </c>
       <c r="K10" s="3">
         <v>282100</v>
@@ -972,25 +972,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>440400</v>
+        <v>417100</v>
       </c>
       <c r="E17" s="3">
-        <v>346400</v>
+        <v>323200</v>
       </c>
       <c r="F17" s="3">
-        <v>320000</v>
+        <v>294800</v>
       </c>
       <c r="G17" s="3">
-        <v>297900</v>
+        <v>267200</v>
       </c>
       <c r="H17" s="3">
-        <v>309600</v>
+        <v>279400</v>
       </c>
       <c r="I17" s="3">
-        <v>281000</v>
+        <v>254100</v>
       </c>
       <c r="J17" s="3">
-        <v>284600</v>
+        <v>268900</v>
       </c>
       <c r="K17" s="3">
         <v>250000</v>
